--- a/input/PL/reg_home_ownership.xlsx
+++ b/input/PL/reg_home_ownership.xlsx
@@ -15,38 +15,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="89" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="108" uniqueCount="61">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Authors:</t>
+  </si>
+  <si>
+    <t>Last edit:</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Process:</t>
+  </si>
+  <si>
+    <t>HO1</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Modelparametersgoverningproje</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
   <si>
     <t>Description:</t>
   </si>
   <si>
-    <t>Model parameters governing projection of home ownership</t>
-  </si>
-  <si>
-    <t>Authors:</t>
-  </si>
-  <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
-    <t>Last edit:</t>
-  </si>
-  <si>
-    <t>12 Jan 2016 AB</t>
-  </si>
-  <si>
-    <t>Process:</t>
-  </si>
-  <si>
-    <t>HO1</t>
-  </si>
-  <si>
     <t>Probit regression estimates of the probability of being a home owner, aged 18+, head of benefit unit</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
     <t>Have combined dhhtp_c4 and lessp_c3 into a single variable with 8 cateogries, dhhtp_c8</t>
   </si>
   <si>
@@ -56,212 +62,152 @@
     <t>Estimated on the sample of benefit unit heads.</t>
   </si>
   <si>
-    <t>Goodness of fit</t>
+    <t>Goodnessoffit</t>
+  </si>
+  <si>
+    <t>HO1 - Home ownership</t>
+  </si>
+  <si>
+    <t>Pseudo R-squared</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Chi^2</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>REGRESSOR</t>
   </si>
   <si>
+    <t>Dgn</t>
+  </si>
+  <si>
+    <t>Dag</t>
+  </si>
+  <si>
+    <t>Dag_sq</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_2_L1</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_3_L1</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_4_L1</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_5_L1</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_6_L1</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_7_L1</t>
+  </si>
+  <si>
+    <t>Dhhtp_c8_8_L1</t>
+  </si>
+  <si>
+    <t>Les_c3_Student_L1</t>
+  </si>
+  <si>
+    <t>Les_c3_NotEmployed_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Na</t>
+  </si>
+  <si>
+    <t>Deh_c4_Medium</t>
+  </si>
+  <si>
+    <t>Deh_c4_Low</t>
+  </si>
+  <si>
+    <t>Dhe_Fair_L1</t>
+  </si>
+  <si>
+    <t>Dhe_Good_L1</t>
+  </si>
+  <si>
+    <t>Dhe_VeryGood_L1</t>
+  </si>
+  <si>
+    <t>Dhe_Excellent_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q2_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q3_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q4_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q5_L1</t>
+  </si>
+  <si>
+    <t>Yptciihs_dv_L1</t>
+  </si>
+  <si>
+    <t>Dhh_owned_L1</t>
+  </si>
+  <si>
+    <t>PL4</t>
+  </si>
+  <si>
+    <t>PL5</t>
+  </si>
+  <si>
+    <t>PL6</t>
+  </si>
+  <si>
+    <t>PL10</t>
+  </si>
+  <si>
+    <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
     <t>COEFFICIENT</t>
-  </si>
-  <si>
-    <t>Dgn</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag_sq</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_2_L1</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_3_L1</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_4_L1</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_5_L1</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_6_L1</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_7_L1</t>
-  </si>
-  <si>
-    <t>Dhhtp_c8_8_L1</t>
-  </si>
-  <si>
-    <t>Les_c3_Student_L1</t>
-  </si>
-  <si>
-    <t>Les_c3_NotEmployed_L1</t>
-  </si>
-  <si>
-    <t>Deh_c4_Na</t>
-  </si>
-  <si>
-    <t>Deh_c4_Medium</t>
-  </si>
-  <si>
-    <t>Deh_c4_Low</t>
-  </si>
-  <si>
-    <t>Dhe_Fair_L1</t>
-  </si>
-  <si>
-    <t>Dhe_Good_L1</t>
-  </si>
-  <si>
-    <t>Dhe_VeryGood_L1</t>
-  </si>
-  <si>
-    <t>Dhe_Excellent_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q2_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q3_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q4_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q5_L1</t>
-  </si>
-  <si>
-    <t>Yptciihs_dv_L1</t>
-  </si>
-  <si>
-    <t>Dhh_owned_L1</t>
-  </si>
-  <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>PL10</t>
-  </si>
-  <si>
-    <t>Year_transformed</t>
-  </si>
-  <si>
-    <t>Y2020</t>
-  </si>
-  <si>
-    <t>Y2021</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>HO1 - Home ownership</t>
-  </si>
-  <si>
-    <t>Pseudo R-squared</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Chi^2</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="17">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -272,7 +218,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -280,100 +226,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,61 +247,99 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
+      <c r="A10" t="s">
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -454,40 +352,90 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>50</v>
-      </c>
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.8940166112438177</v>
       </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1">
         <v>23902.768284529335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
         <v>157181</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
       <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1">
         <v>-7996461.1087994799</v>
       </c>
     </row>
@@ -497,3647 +445,3644 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="N1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="R1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="T1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="U1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="V1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="W1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="X1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="Y1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="Z1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AA1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AB1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AC1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AD1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="AE1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AG1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="AH1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="AI1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1">
         <v>-0.018978040966399205</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.00099387394340359281</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1.4371226888129952e-05</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>-8.7580450511272699e-08</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-0.00040633312487666547</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-0.00047329577684012011</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-0.00015446548117382242</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-0.00040678949289125853</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>-0.00040923054034019344</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-0.00011442103316567514</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>0.00034390265644823045</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>0.00039936083424298104</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>0.00014368262552409672</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-0.00014900584617803851</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-0.00014612317192768521</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>2.0092935939117424e-06</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-0.00012182708109122138</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-9.2855538432787632e-05</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-0.00011367092025852969</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-0.00013389086527852047</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>-1.0003303556687428e-05</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>7.5319701528899332e-05</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="1">
         <v>0.00016514597768344126</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>6.2081385457103048e-05</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="1">
         <v>1.2608306667508067e-05</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="1">
         <v>2.8026226055873204e-05</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="1">
         <v>0.00014473976573825401</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="1">
         <v>3.5578532554783777e-05</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
         <v>0.00010017569509707253</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="1">
         <v>0.00012698498716849719</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="1">
         <v>3.8289557714380861e-06</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="1">
         <v>0.00029053347192074439</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="1">
         <v>-7.9737416356212554e-06</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="1">
         <v>-0.00097644030899550211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.0016286803671730406</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1.4371226888129952e-05</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2.8355522667601062e-05</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-2.5698835065527932e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>6.3811954285429855e-05</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-1.1905526631339166e-05</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>2.400027810188788e-05</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>9.1377430344275314e-05</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-1.7583909791692609e-05</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>1.5979466210300837e-05</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>4.8355513473169942e-06</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>0.00016218453824853217</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>2.2411985593646748e-05</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-3.090629764569713e-05</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-4.1463022345556198e-05</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-2.3840720427480925e-05</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-3.6463173246702364e-05</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-6.2735844983758489e-05</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-3.5643408542784263e-05</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>5.5156281951700213e-05</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-2.1727266472548783e-06</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>6.7277519933091399e-06</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>-2.952768060798355e-05</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="1">
         <v>-5.0242839641659082e-05</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="1">
         <v>-1.2527149712922273e-06</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="1">
         <v>-6.6709038196880799e-06</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="1">
         <v>-1.3264980303597006e-05</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="1">
         <v>-5.3062876237114213e-06</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="1">
         <v>3.6125963610866648e-06</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="1">
         <v>4.4307428989090122e-06</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="1">
         <v>8.327703764781196e-07</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="1">
         <v>-3.0673630053221776e-05</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="1">
         <v>-4.2512818301523793e-06</v>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="1">
         <v>-0.00065493827515274313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1">
         <v>-6.2332458851662092e-06</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>-8.7580450511272699e-08</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-2.5698835065527932e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>2.437377049118211e-09</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>-5.0542503255296981e-07</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-2.9457605505482735e-08</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-1.5924169774058711e-07</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-7.4677945741031516e-07</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.9443248230655444e-07</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-1.4108194419545534e-07</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>9.1859690014996735e-08</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-1.3458850750256883e-06</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-3.1922001628579699e-07</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>3.094790408370396e-07</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>3.8758203381789655e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>1.3147340703200908e-07</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>3.5762934884264015e-07</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>6.625909879163368e-07</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>4.4219365327360015e-07</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-2.7202588395398619e-07</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>9.5019188676706353e-08</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>-6.6271231270129013e-09</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="1">
         <v>3.0537752251226399e-07</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="1">
         <v>4.7885872374676803e-07</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="1">
         <v>1.2993045031016329e-08</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="1">
         <v>2.0538781655068834e-08</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="1">
         <v>1.9969048769535166e-07</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="1">
         <v>1.1443371907865055e-08</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="1">
         <v>-2.6051482032770965e-08</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="1">
         <v>-5.4756373562146035e-08</v>
       </c>
-      <c r="AF4">
+      <c r="AF4" s="1">
         <v>-7.5066633191505373e-09</v>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="1">
         <v>4.2526880862022327e-07</v>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="1">
         <v>2.5648708070154544e-08</v>
       </c>
-      <c r="AI4">
+      <c r="AI4" s="1">
         <v>5.5172826457308151e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.25091983893085629</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-0.00040633312487666547</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>6.3811954285429855e-05</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-5.0542503255296981e-07</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.073878061401730546</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.0056937406613612124</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>0.0059513582322316657</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>0.0064991285616939221</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>0.0059773318404290525</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0.0058468560436968301</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>0.0064300896370810892</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>0.00073424118047140654</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>0.00096175172736609861</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>0.0011476959714615278</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>0.00058425086725378823</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>0.00057182870529315756</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>0.0001129376818885309</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>-7.5046875407683246e-05</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>0.00024022897330650635</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>7.6786432444831375e-05</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>0.00011761054067218756</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>0.0012877083042499371</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="1">
         <v>0.001172418791740213</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="1">
         <v>0.0023250444153020342</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="1">
         <v>-0.00049513511721608846</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="1">
         <v>-0.00014734162456149155</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="1">
         <v>0.00031806354498729959</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="1">
         <v>1.8479556078020501e-05</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="1">
         <v>-0.00019587225271762226</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="1">
         <v>-0.00039207282882377744</v>
       </c>
-      <c r="AF5">
+      <c r="AF5" s="1">
         <v>3.2927125684640408e-06</v>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="1">
         <v>-0.00043790253921358567</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="1">
         <v>0.00035712531434251666</v>
       </c>
-      <c r="AI5">
+      <c r="AI5" s="1">
         <v>-0.0088304270092624329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.002170363043938296</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-0.00047329577684012011</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-1.1905526631339166e-05</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-2.9457605505482735e-08</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.0056937406613612124</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0074837251365506867</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.0058813298561482992</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>0.0057293122074244477</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>0.0062212361673602201</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0.0062256692565504576</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>0.0058984770531300785</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>0.000339454310134446</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>0.00075744417369766922</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>0.00018407127038197414</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>0.00013496288915967858</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>0.00045202473805156657</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>0.00022349008737809143</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-0.00015229546612029101</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>0.00044571511058429347</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>0.00012402411016987488</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>-0.00011818275501193653</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>0.00068617329337322414</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="1">
         <v>0.00090656823247630769</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="1">
         <v>0.0026441179956849404</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="1">
         <v>-0.00013075669042775942</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="1">
         <v>-0.00021046217724854469</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="1">
         <v>0.00013665053968602231</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="1">
         <v>0.00026565314344756223</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="1">
         <v>5.0981317755769266e-05</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="1">
         <v>-0.00021316255195358096</v>
       </c>
-      <c r="AF6">
+      <c r="AF6" s="1">
         <v>1.0112913579604708e-06</v>
       </c>
-      <c r="AG6">
+      <c r="AG6" s="1">
         <v>-0.0009166732263161349</v>
       </c>
-      <c r="AH6">
+      <c r="AH6" s="1">
         <v>0.0002505017626687273</v>
       </c>
-      <c r="AI6">
+      <c r="AI6" s="1">
         <v>-0.00632582452144426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.031671589182149171</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-0.00015446548117382242</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>2.400027810188788e-05</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-1.5924169774058711e-07</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.0059513582322316657</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.0058813298561482992</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.0093632526343332932</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.0059657659872860381</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>0.0061535015510706063</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0.0057982790027322588</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>0.0061385918517395301</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>0.00085683762483812259</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>0.00070197732687710384</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>-0.00021781621619033475</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>-0.00021860185548677681</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-0.00012584217408784888</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>0.00010526795324906609</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-0.00018263132377703924</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>0.00010831760621640962</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>0.00068249603439267566</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>2.6789472273367593e-05</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>0.00052184473274218988</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="1">
         <v>8.6350888347393705e-05</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="1">
         <v>0.0021828889477775435</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="1">
         <v>-0.00015529013550802482</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="1">
         <v>4.0332915867567353e-05</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="1">
         <v>0.00096877449619313426</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="1">
         <v>0.00016874428694269852</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="1">
         <v>0.00018086166899098182</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="1">
         <v>-0.00041316721847588223</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="1">
         <v>-6.3657007581791698e-08</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="1">
         <v>0.00062177103059826103</v>
       </c>
-      <c r="AH7">
+      <c r="AH7" s="1">
         <v>0.00033248036523372479</v>
       </c>
-      <c r="AI7">
+      <c r="AI7" s="1">
         <v>-0.0072946822883686721</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1">
         <v>1.1290532678048155</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-0.00040678949289125853</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>9.1377430344275314e-05</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-7.4677945741031516e-07</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.0064991285616939221</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>0.0057293122074244477</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.0059657659872860381</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.26939706809254066</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.006153782755402324</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0.0056308613428435019</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>0.0061810694815984599</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>0.0025629788632282905</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>0.0016736843701103251</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-0.0001383508904928229</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>-0.00030349626027816783</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-0.00010464805658014914</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>9.0846738195028004e-05</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>-0.0001002375535848058</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>0.00035949328799525125</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>0.00038007129700666975</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>6.4637520855786871e-05</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>0.0012750277321393355</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="1">
         <v>0.0021071237543562084</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="1">
         <v>0.00306981665170391</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="1">
         <v>-0.00037469485640399754</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="1">
         <v>0.00019632930183729048</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="1">
         <v>0.00088218049113759651</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="1">
         <v>6.4498888741546141e-05</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="1">
         <v>1.637863087826819e-06</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="1">
         <v>-0.00037063510459675012</v>
       </c>
-      <c r="AF8">
+      <c r="AF8" s="1">
         <v>3.8362050433558327e-05</v>
       </c>
-      <c r="AG8">
+      <c r="AG8" s="1">
         <v>-0.0008515395638892722</v>
       </c>
-      <c r="AH8">
+      <c r="AH8" s="1">
         <v>-8.5585419456858138e-05</v>
       </c>
-      <c r="AI8">
+      <c r="AI8" s="1">
         <v>-0.010371243575013237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1">
         <v>-0.083040117855668449</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>-0.00040923054034019344</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-1.7583909791692609e-05</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>1.9443248230655444e-07</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.0059773318404290525</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>0.0062212361673602201</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>0.0061535015510706063</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.006153782755402324</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0085713336806794785</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.0059707875798854643</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.006237832926617207</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.0011581806136385184</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>0.00099344239100859506</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>0.00019008468827232095</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>0.00021601783211411046</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>0.00025159588310010635</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>0.00010894524705609503</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>-4.0209065564001203e-05</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>0.00017710062380050162</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-1.540002118004995e-05</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>5.4899319990231758e-05</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>0.00062871183082789314</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="1">
         <v>0.001235504557170591</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="1">
         <v>0.0030360250375524051</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="1">
         <v>-0.00018404270044138218</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="1">
         <v>-0.00012098624353921224</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="1">
         <v>0.00042395949389167345</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="1">
         <v>-5.7463848994823014e-05</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="1">
         <v>-1.9131045944232309e-05</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="1">
         <v>-0.00034894400126846636</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="1">
         <v>-1.3567487343094618e-06</v>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="1">
         <v>-0.00049446879881790209</v>
       </c>
-      <c r="AH9">
+      <c r="AH9" s="1">
         <v>0.00024955917687056659</v>
       </c>
-      <c r="AI9">
+      <c r="AI9" s="1">
         <v>-0.0067096146980991827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1">
         <v>-0.19548895608926464</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-0.00011442103316567514</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>1.5979466210300837e-05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-1.4108194419545534e-07</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>0.0058468560436968301</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>0.0062256692565504576</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>0.0057982790027322588</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>0.0056308613428435019</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.0059707875798854643</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0064911396099878657</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0060940206380014411</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.00023356565842875014</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>0.00026152285819379135</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>0.0001390439137937961</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>0.00018153076060948496</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>0.00032449186194769865</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-3.4321162125766939e-05</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-0.00023254338244185118</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>0.00025842742882159475</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-7.9311011911039741e-05</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>8.2056524376036897e-05</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.00058651584047244177</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="1">
         <v>0.00063656639053241877</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="1">
         <v>0.0022140911693825172</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="1">
         <v>-0.00014215680260620518</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="1">
         <v>-0.00025330587199147691</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="1">
         <v>0.00039548623612149</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="1">
         <v>0.00018535987691865223</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="1">
         <v>0.00018303884585257798</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="1">
         <v>-0.00015781262328585437</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="1">
         <v>-5.4264410631005375e-06</v>
       </c>
-      <c r="AG10">
+      <c r="AG10" s="1">
         <v>-0.00046473275980645455</v>
       </c>
-      <c r="AH10">
+      <c r="AH10" s="1">
         <v>0.00032532800921541169</v>
       </c>
-      <c r="AI10">
+      <c r="AI10" s="1">
         <v>-0.006976367465777184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.2814080227725026</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>0.00034390265644823045</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>4.8355513473169942e-06</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>9.1859690014996735e-08</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>0.0064300896370810892</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>0.0058984770531300785</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>0.0061385918517395301</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>0.0061810694815984599</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.006237832926617207</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0060940206380014411</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.011197320056292679</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.0014802890000286473</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>0.00090137450133307871</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>0.00041468629087946661</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>0.00029705401781914107</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>0.0004006062809501611</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>0.00010800785784853789</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-0.00012307653925583677</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>0.00018550720927286749</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>0.00022868308476124352</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-5.6035799621273778e-05</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>0.00090907641090961448</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="1">
         <v>0.0014105449101244837</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="1">
         <v>0.0030578820781310689</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="1">
         <v>-0.00040063500461692462</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="1">
         <v>-0.00016201287445076473</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="1">
         <v>0.00035661542114304732</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="1">
         <v>0.00015305651190697812</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="1">
         <v>0.00013912888870218489</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="1">
         <v>-0.00031577366222776599</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="1">
         <v>-2.5925933667826748e-05</v>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="1">
         <v>-0.00011740454203951894</v>
       </c>
-      <c r="AH11">
+      <c r="AH11" s="1">
         <v>0.00033718883877941884</v>
       </c>
-      <c r="AI11">
+      <c r="AI11" s="1">
         <v>-0.007675667739505317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.27829219977561798</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>0.00039936083424298104</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>0.00016218453824853217</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-1.3458850750256883e-06</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>0.00073424118047140654</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>0.000339454310134446</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>0.00085683762483812259</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>0.0025629788632282905</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>0.0011581806136385184</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.00023356565842875014</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.0014802890000286473</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.015767934520974823</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>0.0057160787175613448</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>-0.0084362631058071211</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-0.00015622027719326042</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-0.00023124660581193019</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>0.00017293327981233618</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>0.0003233019453075523</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>0.00022053424798149112</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>0.00015918207644917675</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>0.00045617605143681897</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>0.0053257332563867157</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="1">
         <v>0.0064166492993141498</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="1">
         <v>0.0064636579734392123</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="1">
         <v>-0.0006255987565392697</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="1">
         <v>-4.68311779639925e-05</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="1">
         <v>0.00016334609633937135</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="1">
         <v>-7.8023493929811095e-05</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="1">
         <v>6.1398362180683716e-06</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="1">
         <v>0.00011661376631082014</v>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="1">
         <v>-1.7920416028537295e-05</v>
       </c>
-      <c r="AG12">
+      <c r="AG12" s="1">
         <v>0.0002055459689613709</v>
       </c>
-      <c r="AH12">
+      <c r="AH12" s="1">
         <v>-0.00037217094191586237</v>
       </c>
-      <c r="AI12">
+      <c r="AI12" s="1">
         <v>-0.010901733283433333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1">
         <v>-0.037475496995291471</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>0.00014368262552409672</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>2.2411985593646748e-05</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-3.1922001628579699e-07</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>0.00096175172736609861</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>0.00075744417369766922</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>0.00070197732687710384</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>0.0016736843701103251</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>0.00099344239100859506</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0.00026152285819379135</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.00090137450133307871</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>0.0057160787175613448</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.0071303569470518198</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.0004468971008205015</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>-6.4147770784553446e-05</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>-0.00010043762407031072</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>0.00029276554286612592</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>0.00046069407197423125</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>0.00078863731677582944</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>0.0008174004012993551</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-0.0001554941269879056</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>0.005679197032208292</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="1">
         <v>0.0066257821796821496</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="1">
         <v>0.0069850373779410408</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="1">
         <v>-0.00059348601883406718</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="1">
         <v>3.8168197749642932e-07</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="1">
         <v>2.6664286406324032e-05</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="1">
         <v>0.00011448494189555567</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="1">
         <v>-0.00019945231754238749</v>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="1">
         <v>-0.00010518206556868644</v>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="1">
         <v>-3.0674945198631289e-05</v>
       </c>
-      <c r="AG13">
+      <c r="AG13" s="1">
         <v>0.00033517238342445181</v>
       </c>
-      <c r="AH13">
+      <c r="AH13" s="1">
         <v>-0.00029585316043955249</v>
       </c>
-      <c r="AI13">
+      <c r="AI13" s="1">
         <v>-0.007374928963632274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1">
         <v>-0.31452149390397977</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-0.00014900584617803851</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-3.090629764569713e-05</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>3.094790408370396e-07</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>0.0011476959714615278</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>0.00018407127038197414</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>-0.00021781621619033475</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-0.0001383508904928229</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>0.00019008468827232095</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>0.0001390439137937961</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>0.00041468629087946661</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>-0.0084362631058071211</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.0004468971008205015</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.017588715123772355</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.0015993640376819917</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>0.001696375039407752</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-1.6086825502887897e-05</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-4.1613551137122617e-05</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>0.0002031708653928009</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>4.0471820874421645e-05</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-0.00058742228609142951</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>0.00021374693704483898</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="1">
         <v>0.00060770327957088675</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="1">
         <v>0.00058485384087293181</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="1">
         <v>5.7036228538126175e-05</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="1">
         <v>-0.00023393053216736316</v>
       </c>
-      <c r="AB14">
+      <c r="AB14" s="1">
         <v>-0.00038088808027649705</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="1">
         <v>0.0010315832408052746</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="1">
         <v>-8.5538706231338946e-05</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="1">
         <v>-0.00017593056291858038</v>
       </c>
-      <c r="AF14">
+      <c r="AF14" s="1">
         <v>-3.5612465340742309e-07</v>
       </c>
-      <c r="AG14">
+      <c r="AG14" s="1">
         <v>0.00010028523614426894</v>
       </c>
-      <c r="AH14">
+      <c r="AH14" s="1">
         <v>0.00030651186997975174</v>
       </c>
-      <c r="AI14">
+      <c r="AI14" s="1">
         <v>-0.0011066573545399738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.098343078951781529</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-0.00014612317192768521</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-4.1463022345556198e-05</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>3.8758203381789655e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0.00058425086725378823</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>0.00013496288915967858</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>-0.00021860185548677681</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>-0.00030349626027816783</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>0.00021601783211411046</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0.00018153076060948496</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>0.00029705401781914107</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-0.00015622027719326042</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>-6.4147770784553446e-05</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.0015993640376819917</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0019092540580086651</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>0.0015536750187821074</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-2.8535279101750606e-05</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>3.6715803544866242e-05</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>9.8180102485421745e-05</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-0.00039827824634217307</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>6.2319060143729539e-05</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-0.00013359459316913903</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="1">
         <v>0.00033005705975812697</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="1">
         <v>0.00039099175025288004</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="1">
         <v>2.3808906606109209e-05</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="1">
         <v>-0.0001766444044579772</v>
       </c>
-      <c r="AB15">
+      <c r="AB15" s="1">
         <v>-6.4700650484618536e-05</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="1">
         <v>0.00012990715286577924</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="1">
         <v>8.7356270788649379e-05</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="1">
         <v>0.00013732959125312778</v>
       </c>
-      <c r="AF15">
+      <c r="AF15" s="1">
         <v>-1.4263170093541027e-05</v>
       </c>
-      <c r="AG15">
+      <c r="AG15" s="1">
         <v>-0.00015281477512836279</v>
       </c>
-      <c r="AH15">
+      <c r="AH15" s="1">
         <v>0.00033837242675971468</v>
       </c>
-      <c r="AI15">
+      <c r="AI15" s="1">
         <v>-0.00043815064940723545</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.17722354150337824</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>2.0092935939117424e-06</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-2.3840720427480925e-05</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>1.3147340703200908e-07</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>0.00057182870529315756</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>0.00045202473805156657</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-0.00012584217408784888</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-0.00010464805658014914</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>0.00025159588310010635</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0.00032449186194769865</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>0.0004006062809501611</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-0.00023124660581193019</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>-0.00010043762407031072</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>0.001696375039407752</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>0.0015536750187821074</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.0026593512635500046</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.00014365070386651617</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.00020745378932613578</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>0.00043066079815881381</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-0.00012140272586070569</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-0.00013557543024470448</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-0.00016459873869252182</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="1">
         <v>0.00053887127929429473</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="1">
         <v>0.00046479947691593915</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="1">
         <v>2.6721656888593735e-05</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="1">
         <v>-0.00018691449682862847</v>
       </c>
-      <c r="AB16">
+      <c r="AB16" s="1">
         <v>-0.00046997028762141909</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="1">
         <v>6.8428450547195407e-05</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="1">
         <v>-5.2366036744173832e-05</v>
       </c>
-      <c r="AE16">
+      <c r="AE16" s="1">
         <v>0.00013315418505617147</v>
       </c>
-      <c r="AF16">
+      <c r="AF16" s="1">
         <v>9.4597575119621932e-06</v>
       </c>
-      <c r="AG16">
+      <c r="AG16" s="1">
         <v>-0.00022987467445250917</v>
       </c>
-      <c r="AH16">
+      <c r="AH16" s="1">
         <v>0.00025240905060002356</v>
       </c>
-      <c r="AI16">
+      <c r="AI16" s="1">
         <v>-0.0013908295099716245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.087547773092296152</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-0.00012182708109122138</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-3.6463173246702364e-05</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>3.5762934884264015e-07</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>0.0001129376818885309</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>0.00022349008737809143</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>0.00010526795324906609</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>9.0846738195028004e-05</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>0.00010894524705609503</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-3.4321162125766939e-05</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>0.00010800785784853789</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>0.00017293327981233618</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>0.00029276554286612592</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-1.6086825502887897e-05</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-2.8535279101750606e-05</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.00014365070386651617</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.0063972551077177845</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.005679725756430663</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>0.0056841426524541121</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>0.0056573353105390089</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-0.00026202586343610217</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>0.00022916446350060467</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="1">
         <v>0.00023490613069033226</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="1">
         <v>0.00029450750621092068</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="1">
         <v>-6.9119302842170476e-05</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="1">
         <v>9.4761024964688041e-05</v>
       </c>
-      <c r="AB17">
+      <c r="AB17" s="1">
         <v>-0.00018285097438040148</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="1">
         <v>-6.3533426353434494e-06</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="1">
         <v>1.198024465940957e-05</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="1">
         <v>2.6821687747957765e-05</v>
       </c>
-      <c r="AF17">
+      <c r="AF17" s="1">
         <v>1.1175102100839001e-05</v>
       </c>
-      <c r="AG17">
+      <c r="AG17" s="1">
         <v>-9.1276585059692911e-05</v>
       </c>
-      <c r="AH17">
+      <c r="AH17" s="1">
         <v>-6.4173502024974377e-05</v>
       </c>
-      <c r="AI17">
+      <c r="AI17" s="1">
         <v>-0.0052211703074221041</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18">
+        <v>43</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.17313251081936026</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-9.2855538432787632e-05</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-6.2735844983758489e-05</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>6.625909879163368e-07</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>-7.5046875407683246e-05</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-0.00015229546612029101</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-0.00018263132377703924</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>-0.0001002375535848058</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>-4.0209065564001203e-05</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-0.00023254338244185118</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-0.00012307653925583677</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>0.0003233019453075523</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>0.00046069407197423125</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-4.1613551137122617e-05</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>3.6715803544866242e-05</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.00020745378932613578</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.005679725756430663</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.0066576214876318159</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>0.006021818444618768</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>0.0058860473103326538</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-0.0001609690476434189</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>0.00034587510313245987</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="1">
         <v>0.00050185787162658089</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="1">
         <v>0.00041524958451469134</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="1">
         <v>-6.5586288346132634e-05</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="1">
         <v>0.000100569986812643</v>
       </c>
-      <c r="AB18">
+      <c r="AB18" s="1">
         <v>-2.7578860637161254e-05</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="1">
         <v>-8.9506655336021174e-05</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="1">
         <v>-9.5253417938826184e-05</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="1">
         <v>5.8010195855389898e-05</v>
       </c>
-      <c r="AF18">
+      <c r="AF18" s="1">
         <v>-8.0161314770928974e-06</v>
       </c>
-      <c r="AG18">
+      <c r="AG18" s="1">
         <v>0.00064017307713420783</v>
       </c>
-      <c r="AH18">
+      <c r="AH18" s="1">
         <v>-7.8044444085001614e-05</v>
       </c>
-      <c r="AI18">
+      <c r="AI18" s="1">
         <v>-0.0048537092461790159</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.15084069655970977</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-0.00011367092025852969</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-3.5643408542784263e-05</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>4.4219365327360015e-07</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>0.00024022897330650635</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>0.00044571511058429347</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>0.00010831760621640962</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>0.00035949328799525125</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>0.00017710062380050162</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0.00025842742882159475</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>0.00018550720927286749</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>0.00022053424798149112</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>0.00078863731677582944</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>0.0002031708653928009</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>9.8180102485421745e-05</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>0.00043066079815881381</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>0.0056841426524541121</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>0.006021818444618768</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.0069034329965538734</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>0.0063726668553011389</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-0.00010828391510049346</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>0.00040613925269901039</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="1">
         <v>0.00043569212072902585</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="1">
         <v>0.00050659046507704579</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="1">
         <v>-5.441439658717892e-05</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="1">
         <v>2.3621567412572585e-05</v>
       </c>
-      <c r="AB19">
+      <c r="AB19" s="1">
         <v>-0.00017995326892205482</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="1">
         <v>-8.511866729975226e-06</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="1">
         <v>-3.6147113339848511e-05</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="1">
         <v>0.0001750714538153249</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="1">
         <v>-1.0404105387958659e-05</v>
       </c>
-      <c r="AG19">
+      <c r="AG19" s="1">
         <v>0.00012325753185290708</v>
       </c>
-      <c r="AH19">
+      <c r="AH19" s="1">
         <v>-0.00012321244688028791</v>
       </c>
-      <c r="AI19">
+      <c r="AI19" s="1">
         <v>-0.0064293516936078099</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1">
         <v>0.086476490154692637</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-0.00013389086527852047</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>5.5156281951700213e-05</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-2.7202588395398619e-07</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>7.6786432444831375e-05</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>0.00012402411016987488</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>0.00068249603439267566</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.00038007129700666975</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-1.540002118004995e-05</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-7.9311011911039741e-05</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>0.00022868308476124352</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>0.00015918207644917675</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>0.0008174004012993551</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>4.0471820874421645e-05</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-0.00039827824634217307</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-0.00012140272586070569</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>0.0056573353105390089</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>0.0058860473103326538</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>0.0063726668553011389</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0085629906526197182</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-0.00013982951284065509</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>0.00058716209601953825</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="1">
         <v>8.6423346006798702e-05</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="1">
         <v>0.0004907097939094128</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="1">
         <v>-9.7979756067570196e-05</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="1">
         <v>0.00012040193092410605</v>
       </c>
-      <c r="AB20">
+      <c r="AB20" s="1">
         <v>0.00011425944553105846</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="1">
         <v>-0.00012651060789588189</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="1">
         <v>-0.00010136721963088953</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="1">
         <v>7.6651912529211979e-05</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="1">
         <v>1.4257414690348733e-05</v>
       </c>
-      <c r="AG20">
+      <c r="AG20" s="1">
         <v>0.00066017423762080793</v>
       </c>
-      <c r="AH20">
+      <c r="AH20" s="1">
         <v>-0.00028140169741311047</v>
       </c>
-      <c r="AI20">
+      <c r="AI20" s="1">
         <v>-0.0087831154917705767</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21">
+        <v>46</v>
+      </c>
+      <c r="B21" s="1">
         <v>-0.037901408188839344</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>-1.0003303556687428e-05</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-2.1727266472548783e-06</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>9.5019188676706353e-08</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0.00011761054067218756</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>-0.00011818275501193653</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>2.6789472273367593e-05</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>6.4637520855786871e-05</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>5.4899319990231758e-05</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>8.2056524376036897e-05</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-5.6035799621273778e-05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>0.00045617605143681897</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-0.0001554941269879056</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-0.00058742228609142951</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>6.2319060143729539e-05</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-0.00013557543024470448</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-0.00026202586343610217</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-0.0001609690476434189</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-0.00010828391510049346</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-0.00013982951284065509</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.001638684398931365</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>0.0007150684640800369</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="1">
         <v>0.00069518266700410876</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="1">
         <v>0.00070066855675164933</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="1">
         <v>4.5513675494078515e-06</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="1">
         <v>-1.6694766340089083e-05</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="1">
         <v>0.00030943394187434665</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="1">
         <v>3.1399794403607229e-05</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="1">
         <v>6.8021397311085973e-05</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="1">
         <v>-3.2780713285561849e-06</v>
       </c>
-      <c r="AF21">
+      <c r="AF21" s="1">
         <v>8.2067231409786934e-06</v>
       </c>
-      <c r="AG21">
+      <c r="AG21" s="1">
         <v>0.00036149354136955124</v>
       </c>
-      <c r="AH21">
+      <c r="AH21" s="1">
         <v>-5.4025118081652555e-05</v>
       </c>
-      <c r="AI21">
+      <c r="AI21" s="1">
         <v>-0.00093710088853768371</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22">
+        <v>47</v>
+      </c>
+      <c r="B22" s="1">
         <v>-0.054448094789120001</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>7.5319701528899332e-05</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>6.7277519933091399e-06</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>-6.6271231270129013e-09</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0.0012877083042499371</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>0.00068617329337322414</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>0.00052184473274218988</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>0.0012750277321393355</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>0.00062871183082789314</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.00058651584047244177</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>0.00090907641090961448</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.0053257332563867157</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>0.005679197032208292</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>0.00021374693704483898</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-0.00013359459316913903</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-0.00016459873869252182</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>0.00022916446350060467</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>0.00034587510313245987</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>0.00040613925269901039</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>0.00058716209601953825</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>0.0007150684640800369</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.006753549721953394</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="1">
         <v>0.0067887441255874001</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="1">
         <v>0.0069658693827089899</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="1">
         <v>-0.00065364029674658275</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="1">
         <v>-1.8324111407593013e-05</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="1">
         <v>0.00012887059132792164</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="1">
         <v>0.0001036283643836987</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="1">
         <v>-8.3269067570213115e-05</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="1">
         <v>-2.9895742779539099e-05</v>
       </c>
-      <c r="AF22">
+      <c r="AF22" s="1">
         <v>-1.0798234549768131e-05</v>
       </c>
-      <c r="AG22">
+      <c r="AG22" s="1">
         <v>0.00046820003757641095</v>
       </c>
-      <c r="AH22">
+      <c r="AH22" s="1">
         <v>-0.00034494290924677053</v>
       </c>
-      <c r="AI22">
+      <c r="AI22" s="1">
         <v>-0.0074419990148097363</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23">
+        <v>48</v>
+      </c>
+      <c r="B23" s="1">
         <v>0.012006614658663907</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>0.00016514597768344126</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>-2.952768060798355e-05</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>3.0537752251226399e-07</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>0.001172418791740213</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>0.00090656823247630769</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>8.6350888347393705e-05</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>0.0021071237543562084</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>0.001235504557170591</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>0.00063656639053241877</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>0.0014105449101244837</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>0.0064166492993141498</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>0.0066257821796821496</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>0.00060770327957088675</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>0.00033005705975812697</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="1">
         <v>0.00053887127929429473</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="1">
         <v>0.00023490613069033226</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <v>0.00050185787162658089</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>0.00043569212072902585</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="1">
         <v>8.6423346006798702e-05</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="1">
         <v>0.00069518266700410876</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>0.0067887441255874001</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="1">
         <v>0.0090445437115411146</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="1">
         <v>0.0082882925977047668</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="1">
         <v>-0.00068491006654609573</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="1">
         <v>-9.2141823886452128e-06</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="1">
         <v>-4.5664312288171832e-05</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="1">
         <v>0.00023691449827226065</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="1">
         <v>-0.00015550807920486842</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="1">
         <v>-4.5214091050278446e-05</v>
       </c>
-      <c r="AF23">
+      <c r="AF23" s="1">
         <v>-2.675062673335941e-05</v>
       </c>
-      <c r="AG23">
+      <c r="AG23" s="1">
         <v>0.00075646370710133123</v>
       </c>
-      <c r="AH23">
+      <c r="AH23" s="1">
         <v>-0.00024474109220122575</v>
       </c>
-      <c r="AI23">
+      <c r="AI23" s="1">
         <v>-0.0079123709643878909</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24">
+        <v>49</v>
+      </c>
+      <c r="B24" s="1">
         <v>0.1479959109618926</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>6.2081385457103048e-05</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>-5.0242839641659082e-05</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>4.7885872374676803e-07</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0.0023250444153020342</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>0.0026441179956849404</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>0.0021828889477775435</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>0.00306981665170391</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>0.0030360250375524051</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0.0022140911693825172</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>0.0030578820781310689</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>0.0064636579734392123</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>0.0069850373779410408</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>0.00058485384087293181</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>0.00039099175025288004</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>0.00046479947691593915</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="1">
         <v>0.00029450750621092068</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <v>0.00041524958451469134</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>0.00050659046507704579</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>0.0004907097939094128</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="1">
         <v>0.00070066855675164933</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>0.0069658693827089899</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="1">
         <v>0.0082882925977047668</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="1">
         <v>0.010937410201393173</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="1">
         <v>-0.00074862735981940276</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="1">
         <v>0.00018257472752850968</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="1">
         <v>0.00049335904987277135</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="1">
         <v>0.00018824048085723955</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>-3.3747351361036553e-05</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="1">
         <v>-0.0001361418731689679</v>
       </c>
-      <c r="AF24">
+      <c r="AF24" s="1">
         <v>-3.7320861947382584e-05</v>
       </c>
-      <c r="AG24">
+      <c r="AG24" s="1">
         <v>0.00081694601023662994</v>
       </c>
-      <c r="AH24">
+      <c r="AH24" s="1">
         <v>-0.0001796823627780446</v>
       </c>
-      <c r="AI24">
+      <c r="AI24" s="1">
         <v>-0.0093203884943013661</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25">
+        <v>50</v>
+      </c>
+      <c r="B25" s="1">
         <v>-0.0053715691473227543</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>1.2608306667508067e-05</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>-1.2527149712922273e-06</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>1.2993045031016329e-08</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>-0.00049513511721608846</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>-0.00013075669042775942</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>-0.00015529013550802482</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>-0.00037469485640399754</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>-0.00018404270044138218</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>-0.00014215680260620518</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>-0.00040063500461692462</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>-0.0006255987565392697</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>-0.00059348601883406718</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>5.7036228538126175e-05</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>2.3808906606109209e-05</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>2.6721656888593735e-05</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="1">
         <v>-6.9119302842170476e-05</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <v>-6.5586288346132634e-05</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>-5.441439658717892e-05</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>-9.7979756067570196e-05</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="1">
         <v>4.5513675494078515e-06</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="1">
         <v>-0.00065364029674658275</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="1">
         <v>-0.00068491006654609573</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="1">
         <v>-0.00074862735981940276</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="1">
         <v>0.00018056233548445223</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="1">
         <v>-1.5420973909160456e-05</v>
       </c>
-      <c r="AB25">
+      <c r="AB25" s="1">
         <v>-1.8659281767414873e-05</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="1">
         <v>1.1994533517649039e-05</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="1">
         <v>8.0104793853514999e-06</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="1">
         <v>1.3280556399872202e-05</v>
       </c>
-      <c r="AF25">
+      <c r="AF25" s="1">
         <v>8.6093288307196914e-06</v>
       </c>
-      <c r="AG25">
+      <c r="AG25" s="1">
         <v>-0.00011085881533082556</v>
       </c>
-      <c r="AH25">
+      <c r="AH25" s="1">
         <v>2.182033467744402e-05</v>
       </c>
-      <c r="AI25">
+      <c r="AI25" s="1">
         <v>0.00065715512698511251</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1">
         <v>4.5097796953487856</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>2.8026226055873204e-05</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>-6.6709038196880799e-06</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>2.0538781655068834e-08</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>-0.00014734162456149155</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>-0.00021046217724854469</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>4.0332915867567353e-05</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>0.00019632930183729048</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>-0.00012098624353921224</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>-0.00025330587199147691</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>-0.00016201287445076473</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>-4.68311779639925e-05</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>3.8168197749642932e-07</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>-0.00023393053216736316</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>-0.0001766444044579772</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>-0.00018691449682862847</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="1">
         <v>9.4761024964688041e-05</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <v>0.000100569986812643</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>2.3621567412572585e-05</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>0.00012040193092410605</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="1">
         <v>-1.6694766340089083e-05</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="1">
         <v>-1.8324111407593013e-05</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="1">
         <v>-9.2141823886452128e-06</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="1">
         <v>0.00018257472752850968</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="1">
         <v>-1.5420973909160456e-05</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="1">
         <v>0.00097697461473856564</v>
       </c>
-      <c r="AB26">
+      <c r="AB26" s="1">
         <v>0.00010270837392956416</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="1">
         <v>3.782686430561601e-06</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="1">
         <v>2.1042794678532315e-05</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="1">
         <v>9.4575752659883903e-06</v>
       </c>
-      <c r="AF26">
+      <c r="AF26" s="1">
         <v>-1.5371304391358238e-05</v>
       </c>
-      <c r="AG26">
+      <c r="AG26" s="1">
         <v>9.6725403659581705e-05</v>
       </c>
-      <c r="AH26">
+      <c r="AH26" s="1">
         <v>-8.1969801774147062e-05</v>
       </c>
-      <c r="AI26">
+      <c r="AI26" s="1">
         <v>0.00026204163557061878</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1">
         <v>-0.028433975381169239</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>0.00014473976573825401</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>-1.3264980303597006e-05</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>1.9969048769535166e-07</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>0.00031806354498729959</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>0.00013665053968602231</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>0.00096877449619313426</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>0.00088218049113759651</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>0.00042395949389167345</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>0.00039548623612149</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>0.00035661542114304732</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>0.00016334609633937135</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>2.6664286406324032e-05</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>-0.00038088808027649705</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>-6.4700650484618536e-05</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>-0.00046997028762141909</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>-0.00018285097438040148</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>-2.7578860637161254e-05</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>-0.00017995326892205482</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>0.00011425944553105846</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="1">
         <v>0.00030943394187434665</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="1">
         <v>0.00012887059132792164</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="1">
         <v>-4.5664312288171832e-05</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="1">
         <v>0.00049335904987277135</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="1">
         <v>-1.8659281767414873e-05</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="1">
         <v>0.00010270837392956416</v>
       </c>
-      <c r="AB27">
+      <c r="AB27" s="1">
         <v>0.0025912005000310167</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="1">
         <v>0.00075900920031722737</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="1">
         <v>0.00079429414661050159</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="1">
         <v>0.00073314055573998915</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" s="1">
         <v>-1.4785904860909476e-05</v>
       </c>
-      <c r="AG27">
+      <c r="AG27" s="1">
         <v>0.0013498639529399099</v>
       </c>
-      <c r="AH27">
+      <c r="AH27" s="1">
         <v>-2.3361718324284937e-05</v>
       </c>
-      <c r="AI27">
+      <c r="AI27" s="1">
         <v>-0.0010273471275651161</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28">
+        <v>53</v>
+      </c>
+      <c r="B28" s="1">
         <v>-0.14547952477049189</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>3.5578532554783777e-05</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>-5.3062876237114213e-06</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>1.1443371907865055e-08</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>1.8479556078020501e-05</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>0.00026565314344756223</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>0.00016874428694269852</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>6.4498888741546141e-05</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>-5.7463848994823014e-05</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>0.00018535987691865223</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>0.00015305651190697812</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>-7.8023493929811095e-05</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>0.00011448494189555567</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>0.0010315832408052746</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>0.00012990715286577924</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>6.8428450547195407e-05</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="1">
         <v>-6.3533426353434494e-06</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <v>-8.9506655336021174e-05</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>-8.511866729975226e-06</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>-0.00012651060789588189</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="1">
         <v>3.1399794403607229e-05</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="1">
         <v>0.0001036283643836987</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="1">
         <v>0.00023691449827226065</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="1">
         <v>0.00018824048085723955</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="1">
         <v>1.1994533517649039e-05</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="1">
         <v>3.782686430561601e-06</v>
       </c>
-      <c r="AB28">
+      <c r="AB28" s="1">
         <v>0.00075900920031722737</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="1">
         <v>0.0029524061091660871</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" s="1">
         <v>0.00075909615534138256</v>
       </c>
-      <c r="AE28">
+      <c r="AE28" s="1">
         <v>0.00076913022353905253</v>
       </c>
-      <c r="AF28">
+      <c r="AF28" s="1">
         <v>-1.4427954052033063e-05</v>
       </c>
-      <c r="AG28">
+      <c r="AG28" s="1">
         <v>-5.1379654474575497e-06</v>
       </c>
-      <c r="AH28">
+      <c r="AH28" s="1">
         <v>-3.0227814925132523e-05</v>
       </c>
-      <c r="AI28">
+      <c r="AI28" s="1">
         <v>-0.00070662813332040826</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1">
         <v>-0.10246897738093121</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>0.00010017569509707253</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>3.6125963610866648e-06</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>-2.6051482032770965e-08</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>-0.00019587225271762226</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>5.0981317755769266e-05</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>0.00018086166899098182</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>1.637863087826819e-06</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>-1.9131045944232309e-05</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0.00018303884585257798</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>0.00013912888870218489</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>6.1398362180683716e-06</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>-0.00019945231754238749</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>-8.5538706231338946e-05</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>8.7356270788649379e-05</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>-5.2366036744173832e-05</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="1">
         <v>1.198024465940957e-05</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <v>-9.5253417938826184e-05</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <v>-3.6147113339848511e-05</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="1">
         <v>-0.00010136721963088953</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="1">
         <v>6.8021397311085973e-05</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="1">
         <v>-8.3269067570213115e-05</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="1">
         <v>-0.00015550807920486842</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="1">
         <v>-3.3747351361036553e-05</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="1">
         <v>8.0104793853514999e-06</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="1">
         <v>2.1042794678532315e-05</v>
       </c>
-      <c r="AB29">
+      <c r="AB29" s="1">
         <v>0.00079429414661050159</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="1">
         <v>0.00075909615534138256</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" s="1">
         <v>0.0016507768118120291</v>
       </c>
-      <c r="AE29">
+      <c r="AE29" s="1">
         <v>0.00076481217866725148</v>
       </c>
-      <c r="AF29">
+      <c r="AF29" s="1">
         <v>-1.269462444398753e-05</v>
       </c>
-      <c r="AG29">
+      <c r="AG29" s="1">
         <v>-8.0209193396061675e-05</v>
       </c>
-      <c r="AH29">
+      <c r="AH29" s="1">
         <v>0.00016099810355147339</v>
       </c>
-      <c r="AI29">
+      <c r="AI29" s="1">
         <v>-0.00071611013572568639</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1">
         <v>-0.026608442149023505</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>0.00012698498716849719</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>4.4307428989090122e-06</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>-5.4756373562146035e-08</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>-0.00039207282882377744</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>-0.00021316255195358096</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>-0.00041316721847588223</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>-0.00037063510459675012</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>-0.00034894400126846636</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>-0.00015781262328585437</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>-0.00031577366222776599</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="1">
         <v>0.00011661376631082014</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="1">
         <v>-0.00010518206556868644</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>-0.00017593056291858038</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>0.00013732959125312778</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="1">
         <v>0.00013315418505617147</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="1">
         <v>2.6821687747957765e-05</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="1">
         <v>5.8010195855389898e-05</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="1">
         <v>0.0001750714538153249</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="1">
         <v>7.6651912529211979e-05</v>
       </c>
-      <c r="V30">
+      <c r="V30" s="1">
         <v>-3.2780713285561849e-06</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="1">
         <v>-2.9895742779539099e-05</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="1">
         <v>-4.5214091050278446e-05</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="1">
         <v>-0.0001361418731689679</v>
       </c>
-      <c r="Z30">
+      <c r="Z30" s="1">
         <v>1.3280556399872202e-05</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="1">
         <v>9.4575752659883903e-06</v>
       </c>
-      <c r="AB30">
+      <c r="AB30" s="1">
         <v>0.00073314055573998915</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="1">
         <v>0.00076913022353905253</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" s="1">
         <v>0.00076481217866725148</v>
       </c>
-      <c r="AE30">
+      <c r="AE30" s="1">
         <v>0.0013873644261254258</v>
       </c>
-      <c r="AF30">
+      <c r="AF30" s="1">
         <v>-6.6631097202843586e-06</v>
       </c>
-      <c r="AG30">
+      <c r="AG30" s="1">
         <v>0.00019576048570816738</v>
       </c>
-      <c r="AH30">
+      <c r="AH30" s="1">
         <v>-2.9120220581617742e-05</v>
       </c>
-      <c r="AI30">
+      <c r="AI30" s="1">
         <v>-0.00074527434068725269</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31">
+        <v>56</v>
+      </c>
+      <c r="B31" s="1">
         <v>0.00208419325274881</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>3.8289557714380861e-06</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>8.327703764781196e-07</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>-7.5066633191505373e-09</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>3.2927125684640408e-06</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>1.0112913579604708e-06</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>-6.3657007581791698e-08</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="1">
         <v>3.8362050433558327e-05</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>-1.3567487343094618e-06</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>-5.4264410631005375e-06</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>-2.5925933667826748e-05</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="1">
         <v>-1.7920416028537295e-05</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="1">
         <v>-3.0674945198631289e-05</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="1">
         <v>-3.5612465340742309e-07</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="1">
         <v>-1.4263170093541027e-05</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="1">
         <v>9.4597575119621932e-06</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="1">
         <v>1.1175102100839001e-05</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="1">
         <v>-8.0161314770928974e-06</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="1">
         <v>-1.0404105387958659e-05</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="1">
         <v>1.4257414690348733e-05</v>
       </c>
-      <c r="V31">
+      <c r="V31" s="1">
         <v>8.2067231409786934e-06</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="1">
         <v>-1.0798234549768131e-05</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="1">
         <v>-2.675062673335941e-05</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="1">
         <v>-3.7320861947382584e-05</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="1">
         <v>8.6093288307196914e-06</v>
       </c>
-      <c r="AA31">
+      <c r="AA31" s="1">
         <v>-1.5371304391358238e-05</v>
       </c>
-      <c r="AB31">
+      <c r="AB31" s="1">
         <v>-1.4785904860909476e-05</v>
       </c>
-      <c r="AC31">
+      <c r="AC31" s="1">
         <v>-1.4427954052033063e-05</v>
       </c>
-      <c r="AD31">
+      <c r="AD31" s="1">
         <v>-1.269462444398753e-05</v>
       </c>
-      <c r="AE31">
+      <c r="AE31" s="1">
         <v>-6.6631097202843586e-06</v>
       </c>
-      <c r="AF31">
+      <c r="AF31" s="1">
         <v>1.7993968866630589e-05</v>
       </c>
-      <c r="AG31">
+      <c r="AG31" s="1">
         <v>-5.2350341329338273e-05</v>
       </c>
-      <c r="AH31">
+      <c r="AH31" s="1">
         <v>-6.7799057735815998e-05</v>
       </c>
-      <c r="AI31">
+      <c r="AI31" s="1">
         <v>-0.00027889866812484074</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32">
+        <v>57</v>
+      </c>
+      <c r="B32" s="1">
         <v>-0.34650559030821959</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>0.00029053347192074439</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>-3.0673630053221776e-05</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>4.2526880862022327e-07</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>-0.00043790253921358567</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>-0.0009166732263161349</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>0.00062177103059826103</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="1">
         <v>-0.0008515395638892722</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>-0.00049446879881790209</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>-0.00046473275980645455</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>-0.00011740454203951894</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="1">
         <v>0.0002055459689613709</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="1">
         <v>0.00033517238342445181</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="1">
         <v>0.00010028523614426894</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="1">
         <v>-0.00015281477512836279</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="1">
         <v>-0.00022987467445250917</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="1">
         <v>-9.1276585059692911e-05</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="1">
         <v>0.00064017307713420783</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="1">
         <v>0.00012325753185290708</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="1">
         <v>0.00066017423762080793</v>
       </c>
-      <c r="V32">
+      <c r="V32" s="1">
         <v>0.00036149354136955124</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="1">
         <v>0.00046820003757641095</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="1">
         <v>0.00075646370710133123</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="1">
         <v>0.00081694601023662994</v>
       </c>
-      <c r="Z32">
+      <c r="Z32" s="1">
         <v>-0.00011085881533082556</v>
       </c>
-      <c r="AA32">
+      <c r="AA32" s="1">
         <v>9.6725403659581705e-05</v>
       </c>
-      <c r="AB32">
+      <c r="AB32" s="1">
         <v>0.0013498639529399099</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="1">
         <v>-5.1379654474575497e-06</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" s="1">
         <v>-8.0209193396061675e-05</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="1">
         <v>0.00019576048570816738</v>
       </c>
-      <c r="AF32">
+      <c r="AF32" s="1">
         <v>-5.2350341329338273e-05</v>
       </c>
-      <c r="AG32">
+      <c r="AG32" s="1">
         <v>0.0064611996510061283</v>
       </c>
-      <c r="AH32">
+      <c r="AH32" s="1">
         <v>0.00026358312433997713</v>
       </c>
-      <c r="AI32">
+      <c r="AI32" s="1">
         <v>0.00015959253374718931</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33">
+        <v>58</v>
+      </c>
+      <c r="B33" s="1">
         <v>-0.12651206701570897</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>-7.9737416356212554e-06</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>-4.2512818301523793e-06</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>2.5648708070154544e-08</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>0.00035712531434251666</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>0.0002505017626687273</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>0.00033248036523372479</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="1">
         <v>-8.5585419456858138e-05</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
         <v>0.00024955917687056659</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>0.00032532800921541169</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="1">
         <v>0.00033718883877941884</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="1">
         <v>-0.00037217094191586237</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="1">
         <v>-0.00029585316043955249</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="1">
         <v>0.00030651186997975174</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="1">
         <v>0.00033837242675971468</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="1">
         <v>0.00025240905060002356</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="1">
         <v>-6.4173502024974377e-05</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="1">
         <v>-7.8044444085001614e-05</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="1">
         <v>-0.00012321244688028791</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="1">
         <v>-0.00028140169741311047</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="1">
         <v>-5.4025118081652555e-05</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="1">
         <v>-0.00034494290924677053</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="1">
         <v>-0.00024474109220122575</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="1">
         <v>-0.0001796823627780446</v>
       </c>
-      <c r="Z33">
+      <c r="Z33" s="1">
         <v>2.182033467744402e-05</v>
       </c>
-      <c r="AA33">
+      <c r="AA33" s="1">
         <v>-8.1969801774147062e-05</v>
       </c>
-      <c r="AB33">
+      <c r="AB33" s="1">
         <v>-2.3361718324284937e-05</v>
       </c>
-      <c r="AC33">
+      <c r="AC33" s="1">
         <v>-3.0227814925132523e-05</v>
       </c>
-      <c r="AD33">
+      <c r="AD33" s="1">
         <v>0.00016099810355147339</v>
       </c>
-      <c r="AE33">
+      <c r="AE33" s="1">
         <v>-2.9120220581617742e-05</v>
       </c>
-      <c r="AF33">
+      <c r="AF33" s="1">
         <v>-6.7799057735815998e-05</v>
       </c>
-      <c r="AG33">
+      <c r="AG33" s="1">
         <v>0.00026358312433997713</v>
       </c>
-      <c r="AH33">
+      <c r="AH33" s="1">
         <v>0.0026743518094546202</v>
       </c>
-      <c r="AI33">
+      <c r="AI33" s="1">
         <v>0.0010060275521800413</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1">
         <v>-1.5763275527330953</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>-0.00097644030899550211</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>-0.00065493827515274313</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>5.5172826457308151e-06</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>-0.0088304270092624329</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>-0.00632582452144426</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>-0.0072946822883686721</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="1">
         <v>-0.010371243575013237</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>-0.0067096146980991827</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>-0.006976367465777184</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>-0.007675667739505317</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="1">
         <v>-0.010901733283433333</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="1">
         <v>-0.007374928963632274</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="1">
         <v>-0.0011066573545399738</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="1">
         <v>-0.00043815064940723545</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="1">
         <v>-0.0013908295099716245</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="1">
         <v>-0.0052211703074221041</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="1">
         <v>-0.0048537092461790159</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="1">
         <v>-0.0064293516936078099</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="1">
         <v>-0.0087831154917705767</v>
       </c>
-      <c r="V34">
+      <c r="V34" s="1">
         <v>-0.00093710088853768371</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="1">
         <v>-0.0074419990148097363</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="1">
         <v>-0.0079123709643878909</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="1">
         <v>-0.0093203884943013661</v>
       </c>
-      <c r="Z34">
+      <c r="Z34" s="1">
         <v>0.00065715512698511251</v>
       </c>
-      <c r="AA34">
+      <c r="AA34" s="1">
         <v>0.00026204163557061878</v>
       </c>
-      <c r="AB34">
+      <c r="AB34" s="1">
         <v>-0.0010273471275651161</v>
       </c>
-      <c r="AC34">
+      <c r="AC34" s="1">
         <v>-0.00070662813332040826</v>
       </c>
-      <c r="AD34">
+      <c r="AD34" s="1">
         <v>-0.00071611013572568639</v>
       </c>
-      <c r="AE34">
+      <c r="AE34" s="1">
         <v>-0.00074527434068725269</v>
       </c>
-      <c r="AF34">
+      <c r="AF34" s="1">
         <v>-0.00027889866812484074</v>
       </c>
-      <c r="AG34">
+      <c r="AG34" s="1">
         <v>0.00015959253374718931</v>
       </c>
-      <c r="AH34">
+      <c r="AH34" s="1">
         <v>0.0010060275521800413</v>
       </c>
-      <c r="AI34">
+      <c r="AI34" s="1">
         <v>0.04428351177748488</v>
       </c>
     </row>
